--- a/artfynd/A 30752-2021 artfynd.xlsx
+++ b/artfynd/A 30752-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30752-2021 artfynd.xlsx
+++ b/artfynd/A 30752-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4245,6 +4245,108 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118889394</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90048</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Källberget (Källberget), Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>543198</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6701464</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30752-2021 artfynd.xlsx
+++ b/artfynd/A 30752-2021 artfynd.xlsx
@@ -4250,7 +4250,7 @@
         <v>118889394</v>
       </c>
       <c r="B32" t="n">
-        <v>90048</v>
+        <v>90055</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 30752-2021 artfynd.xlsx
+++ b/artfynd/A 30752-2021 artfynd.xlsx
@@ -4235,7 +4235,7 @@
         <v>127134489</v>
       </c>
       <c r="B32" t="n">
-        <v>92569</v>
+        <v>92643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>127134559</v>
       </c>
       <c r="B33" t="n">
-        <v>92547</v>
+        <v>92621</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>127134770</v>
       </c>
       <c r="B34" t="n">
-        <v>90790</v>
+        <v>90864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>127135005</v>
       </c>
       <c r="B35" t="n">
-        <v>92569</v>
+        <v>92643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
